--- a/results/Int Task Remove ACC -0.5/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.5/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.01322943022524191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01495791281435668</v>
+        <v>0.01495188965889931</v>
       </c>
       <c r="F3" t="n">
         <v>0.0001461545866656776</v>
@@ -1166,10 +1166,10 @@
         <v>0.02504548641818673</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.06130934779159e-05</v>
+        <v>-8.968903644691501e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.862274083454634e-05</v>
+        <v>6.170820828286466e-05</v>
       </c>
       <c r="J3" t="n">
         <v>0.03778950789780806</v>
@@ -1178,16 +1178,16 @@
         <v>0.02128168514198201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02128168514198201</v>
+        <v>0.02127865850759944</v>
       </c>
       <c r="M3" t="n">
         <v>0.01628142467095929</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01288399643653465</v>
+        <v>0.01288418645683766</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02023002569421398</v>
+        <v>0.02023309223821889</v>
       </c>
       <c r="P3" t="n">
         <v>0.003052785150718803</v>
@@ -1196,7 +1196,7 @@
         <v>0.007240306517753539</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01474636078999333</v>
+        <v>0.01473411792912835</v>
       </c>
       <c r="S3" t="n">
         <v>0.3038590963853577</v>
@@ -1208,7 +1208,7 @@
         <v>0.1308317241964634</v>
       </c>
       <c r="V3" t="n">
-        <v>7.082872109132281e-05</v>
+        <v>6.457969780624407e-05</v>
       </c>
       <c r="W3" t="n">
         <v>0.005695964031890531</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07949853167978144</v>
+        <v>0.07950149552091955</v>
       </c>
       <c r="AK3" t="n">
         <v>0.08306458411404723</v>
@@ -1298,7 +1298,7 @@
         <v>-0.0004427934456047656</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.005510496050012163</v>
+        <v>0.005507373001917223</v>
       </c>
       <c r="BA3" t="n">
         <v>-0.001560281258288521</v>
@@ -1307,10 +1307,10 @@
         <v>0.003601982940574905</v>
       </c>
       <c r="BC3" t="n">
+        <v>4.191233141505714e-05</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.598464913882717e-05</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.191233141505714e-05</v>
       </c>
       <c r="BE3" t="n">
         <v>0.0004039090277808088</v>
@@ -1340,7 +1340,7 @@
         <v>0.02370200332816175</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.001557307722754771</v>
+        <v>-0.001560281258288521</v>
       </c>
       <c r="BO3" t="n">
         <v>0.014899406404332</v>
@@ -1364,7 +1364,7 @@
         <v>0.04381121132369126</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0009691705617547411</v>
+        <v>-0.000966197026220992</v>
       </c>
       <c r="BW3" t="n">
         <v>0.006042850707788125</v>
@@ -1385,7 +1385,7 @@
         <v>0.0002691714352787156</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0006116561616974414</v>
+        <v>-0.0006056189058334172</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.001265576372168853</v>
@@ -1394,7 +1394,7 @@
         <v>0.0007457990986872421</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001187581007325944</v>
+        <v>-0.001190704055420884</v>
       </c>
       <c r="CG3" t="n">
         <v>0.002229864098279526</v>
@@ -1428,7 +1428,7 @@
         <v>0.03068950553140626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01773245884427731</v>
+        <v>0.0177363771511276</v>
       </c>
       <c r="F4" t="n">
         <v>0.007670128929002182</v>
@@ -1437,10 +1437,10 @@
         <v>0.03050741353007814</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00269879735680364</v>
+        <v>0.002701015325166672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008933005753109721</v>
+        <v>0.0008915878603777253</v>
       </c>
       <c r="J4" t="n">
         <v>0.03593194334692156</v>
@@ -1449,16 +1449,16 @@
         <v>0.02466970478358587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02466970478358587</v>
+        <v>0.0246641202128747</v>
       </c>
       <c r="M4" t="n">
         <v>0.01935765249360972</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01468400303209422</v>
+        <v>0.0146789878500944</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0273535102885577</v>
+        <v>0.02735314262412688</v>
       </c>
       <c r="P4" t="n">
         <v>0.02067305666760824</v>
@@ -1467,7 +1467,7 @@
         <v>0.02020277460742051</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01868375933871073</v>
+        <v>0.01868656817869368</v>
       </c>
       <c r="S4" t="n">
         <v>0.07851427473211192</v>
@@ -1479,7 +1479,7 @@
         <v>0.05630917750316831</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008941434804307542</v>
+        <v>0.0008971998906994385</v>
       </c>
       <c r="W4" t="n">
         <v>0.02273168053452069</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.05600283183860708</v>
+        <v>0.05600545504580928</v>
       </c>
       <c r="AK4" t="n">
         <v>0.04700249663095493</v>
@@ -1569,7 +1569,7 @@
         <v>0.02215854373615537</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.01390057589769383</v>
+        <v>0.01390180683000377</v>
       </c>
       <c r="BA4" t="n">
         <v>0.009761770993238298</v>
@@ -1578,10 +1578,10 @@
         <v>0.03093800706225815</v>
       </c>
       <c r="BC4" t="n">
+        <v>0.0009547571906597221</v>
+      </c>
+      <c r="BD4" t="n">
         <v>0.0009552302145599836</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.0009547571906597221</v>
       </c>
       <c r="BE4" t="n">
         <v>0.001207426055080433</v>
@@ -1611,7 +1611,7 @@
         <v>0.03646300047014741</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.009762736317151551</v>
+        <v>0.009761770993238298</v>
       </c>
       <c r="BO4" t="n">
         <v>0.01550790954464149</v>
@@ -1635,7 +1635,7 @@
         <v>0.05117900131622871</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02034018772498189</v>
+        <v>0.02033932817220305</v>
       </c>
       <c r="BW4" t="n">
         <v>0.027255960009516</v>
@@ -1656,7 +1656,7 @@
         <v>0.0009782519644185614</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002847233521912692</v>
+        <v>0.002849643547079151</v>
       </c>
       <c r="CD4" t="n">
         <v>0.006968728754243584</v>
@@ -1665,7 +1665,7 @@
         <v>0.004232641038900926</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.02016088521160772</v>
+        <v>0.02016038220148033</v>
       </c>
       <c r="CG4" t="n">
         <v>0.03287940116744349</v>
@@ -1726,7 +1726,7 @@
         <v>-0.01468682505399568</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01363492565643781</v>
+        <v>-0.01360329009807021</v>
       </c>
       <c r="O5" t="n">
         <v>-0.01154697880417587</v>
@@ -1970,7 +1970,7 @@
         <v>-0.01076102142982255</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002750136487505614</v>
+        <v>0.002742653697921657</v>
       </c>
       <c r="F6" t="n">
         <v>-0.006297675701868568</v>
@@ -1979,7 +1979,7 @@
         <v>0.003894351552665478</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0003079487681264259</v>
+        <v>-0.0003156624367472216</v>
       </c>
       <c r="I6" t="n">
         <v>-0.0003103321078815613</v>
@@ -2120,10 +2120,10 @@
         <v>-0.01202833957521957</v>
       </c>
       <c r="BC6" t="n">
+        <v>-0.0002898335315101169</v>
+      </c>
+      <c r="BD6" t="n">
         <v>-0.0003046527372006919</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.0002898335315101169</v>
       </c>
       <c r="BE6" t="n">
         <v>-8.421794026258478e-05</v>
@@ -2177,7 +2177,7 @@
         <v>0.009498696520743236</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.01223064045067395</v>
+        <v>-0.01222320661183958</v>
       </c>
       <c r="BW6" t="n">
         <v>8.323244552059239e-05</v>
@@ -2241,7 +2241,7 @@
         <v>0.008734693274818274</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01633194559223284</v>
+        <v>0.01634727831225738</v>
       </c>
       <c r="F7" t="n">
         <v>0.002561934787114517</v>
@@ -2268,10 +2268,10 @@
         <v>0.01273509771664104</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01419614282927941</v>
+        <v>0.01418127515161066</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01547879440285735</v>
+        <v>0.01549412712288189</v>
       </c>
       <c r="P7" t="n">
         <v>0.005933707938628641</v>
@@ -2280,7 +2280,7 @@
         <v>0.005655236201575009</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007246891318858972</v>
+        <v>0.007201292255008773</v>
       </c>
       <c r="S7" t="n">
         <v>0.317863422181588</v>
@@ -2292,7 +2292,7 @@
         <v>0.1301681772480598</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0002492039936666524</v>
+        <v>-0.0002650217728504545</v>
       </c>
       <c r="W7" t="n">
         <v>0.0001017134654926026</v>
@@ -2382,7 +2382,7 @@
         <v>0.001417314117345814</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0004793379708458556</v>
+        <v>0.0004637227303711522</v>
       </c>
       <c r="BA7" t="n">
         <v>-8.955757171978391e-05</v>
@@ -2469,7 +2469,7 @@
         <v>3.066544004908245e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0002817798307392982</v>
+        <v>0.0002970005308915058</v>
       </c>
       <c r="CD7" t="n">
         <v>-0.0002811584044857707</v>
@@ -2478,7 +2478,7 @@
         <v>0.001621354364105598</v>
       </c>
       <c r="CF7" t="n">
-        <v>-6.084245491305706e-05</v>
+        <v>-7.645769538776044e-05</v>
       </c>
       <c r="CG7" t="n">
         <v>0.005724696504757204</v>
@@ -2512,7 +2512,7 @@
         <v>0.0449100021716102</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02186771433118978</v>
+        <v>0.02186028049235541</v>
       </c>
       <c r="F8" t="n">
         <v>0.004692023064631149</v>
@@ -2521,7 +2521,7 @@
         <v>0.05301536816389325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004158628583833645</v>
+        <v>0.0004084532555380771</v>
       </c>
       <c r="I8" t="n">
         <v>0.0005061630666331252</v>
@@ -2551,7 +2551,7 @@
         <v>0.01991731052795202</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02148418114950913</v>
+        <v>0.02147637352927177</v>
       </c>
       <c r="S8" t="n">
         <v>0.3629940793708716</v>
@@ -2695,7 +2695,7 @@
         <v>0.04444583501227303</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001348578012828705</v>
+        <v>0.00134114417399433</v>
       </c>
       <c r="BO8" t="n">
         <v>0.02626803250191516</v>
@@ -2804,7 +2804,7 @@
         <v>0.06225786924939471</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06225786924939471</v>
+        <v>0.06222760290556904</v>
       </c>
       <c r="M9" t="n">
         <v>0.04418886198547221</v>
